--- a/resources/report/60/95/rpt_6095180.xlsx
+++ b/resources/report/60/95/rpt_6095180.xlsx
@@ -83,9 +83,6 @@
     <t>Tổng số hóa đơn trên bảng kê:$[L_COUNT_ORDER] hóa đơn</t>
   </si>
   <si>
-    <t>ORDERBY_NO</t>
-  </si>
-  <si>
     <t>FORM_NO</t>
   </si>
   <si>
@@ -131,7 +128,10 @@
     <t>REMARK</t>
   </si>
   <si>
-    <t>CANCEL_BY</t>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>REL_BY</t>
   </si>
 </sst>
 </file>
@@ -333,37 +333,79 @@
   </cellStyleXfs>
   <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -383,48 +425,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -712,321 +712,324 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="11.140625" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23" customWidth="1"/>
     <col min="12" max="12" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="2" t="s">
+      <c r="A1" s="14"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
     </row>
     <row r="5" spans="1:17" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="6"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="16"/>
+      <c r="O5" s="16"/>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16"/>
     </row>
     <row r="6" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="30"/>
-      <c r="C6" s="30"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="30"/>
-      <c r="J6" s="30"/>
-      <c r="K6" s="30"/>
-      <c r="L6" s="30"/>
-      <c r="M6" s="30"/>
-      <c r="N6" s="30"/>
-      <c r="O6" s="30"/>
-      <c r="P6" s="30"/>
-      <c r="Q6" s="30"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="13"/>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="13"/>
     </row>
     <row r="7" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="31" t="s">
+      <c r="A7" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="31"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="31"/>
-      <c r="M7" s="31"/>
-      <c r="N7" s="31"/>
-      <c r="O7" s="31"/>
-      <c r="P7" s="31"/>
-      <c r="Q7" s="31"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="17"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="17"/>
+      <c r="Q7" s="17"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8" t="s">
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="9" t="s">
+      <c r="H8" s="21"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="21"/>
+      <c r="L8" s="21"/>
+      <c r="M8" s="21"/>
+      <c r="N8" s="21"/>
+      <c r="O8" s="21"/>
+      <c r="P8" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="Q8" s="10" t="s">
+      <c r="Q8" s="25" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="11"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="12" t="s">
+      <c r="A9" s="19"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="14"/>
-      <c r="L9" s="15" t="s">
+      <c r="H9" s="27"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="27"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="M9" s="16"/>
-      <c r="N9" s="16"/>
-      <c r="O9" s="17"/>
-      <c r="P9" s="18"/>
-      <c r="Q9" s="10"/>
+      <c r="M9" s="30"/>
+      <c r="N9" s="30"/>
+      <c r="O9" s="31"/>
+      <c r="P9" s="23"/>
+      <c r="Q9" s="25"/>
     </row>
     <row r="10" spans="1:17" ht="42.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="19"/>
-      <c r="B10" s="20" t="s">
+      <c r="A10" s="20"/>
+      <c r="B10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="20" t="s">
+      <c r="D10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="20" t="s">
+      <c r="F10" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G10" s="20" t="s">
+      <c r="G10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H10" s="20" t="s">
+      <c r="H10" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="I10" s="20" t="s">
+      <c r="I10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="J10" s="20" t="s">
+      <c r="J10" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="K10" s="20" t="s">
+      <c r="K10" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="L10" s="21" t="s">
+      <c r="L10" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="M10" s="21" t="s">
+      <c r="M10" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="N10" s="21" t="s">
+      <c r="N10" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="O10" s="21" t="s">
+      <c r="O10" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P10" s="22"/>
-      <c r="Q10" s="10"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="25"/>
     </row>
     <row r="11" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="C11" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="D11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="23" t="s">
+      <c r="E11" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="23" t="s">
+      <c r="F11" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="24" t="s">
+      <c r="G11" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="23" t="s">
+      <c r="H11" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H11" s="23" t="s">
+      <c r="I11" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="I11" s="25" t="s">
+      <c r="J11" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="J11" s="25" t="s">
+      <c r="K11" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="K11" s="24" t="s">
+      <c r="L11" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="L11" s="24" t="s">
+      <c r="M11" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="M11" s="27" t="s">
+      <c r="N11" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="N11" s="28" t="s">
+      <c r="O11" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="O11" s="27" t="s">
+      <c r="P11" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q11" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="P11" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q11" s="29" t="s">
-        <v>35</v>
-      </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="23"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="23"/>
-      <c r="I12" s="25"/>
-      <c r="J12" s="25"/>
-      <c r="K12" s="24"/>
-      <c r="L12" s="26"/>
-      <c r="M12" s="27"/>
-      <c r="N12" s="28"/>
-      <c r="O12" s="27"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="29"/>
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="10"/>
+      <c r="P12" s="6"/>
+      <c r="Q12" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -1038,12 +1041,12 @@
     <mergeCell ref="Q8:Q10"/>
     <mergeCell ref="G9:K9"/>
     <mergeCell ref="L9:O9"/>
+    <mergeCell ref="A6:Q6"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="O1:Q1"/>
     <mergeCell ref="A2:O2"/>
     <mergeCell ref="A3:L3"/>
     <mergeCell ref="A5:Q5"/>
-    <mergeCell ref="A6:Q6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/resources/report/60/95/rpt_6095180.xlsx
+++ b/resources/report/60/95/rpt_6095180.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+  <workbookPr filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="39">
   <si>
     <t>Mẫu : 03</t>
   </si>
@@ -132,12 +132,18 @@
   </si>
   <si>
     <t>REL_BY</t>
+  </si>
+  <si>
+    <t>Lý do</t>
+  </si>
+  <si>
+    <t>CANCEL_REASON</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="####;\-####"/>
@@ -331,7 +337,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -369,6 +375,54 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -380,51 +434,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -708,77 +717,80 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:R12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="11.140625" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="11.109375" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="23" customWidth="1"/>
-    <col min="12" max="12" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="14"/>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="15" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A1" s="30"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="14"/>
-      <c r="N2" s="14"/>
-      <c r="O2" s="14"/>
+      <c r="P1" s="31"/>
+      <c r="Q1" s="31"/>
+      <c r="R1" s="31"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" s="30"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
       <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="14"/>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="1"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A3" s="30"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
+      <c r="K3" s="30"/>
+      <c r="L3" s="30"/>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
-      <c r="Q3" s="1"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q3" s="13"/>
+      <c r="R3" s="1"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -795,125 +807,133 @@
       <c r="N4" s="2"/>
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
-    </row>
-    <row r="5" spans="1:17" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+      <c r="Q4" s="13"/>
+      <c r="R4" s="1"/>
+    </row>
+    <row r="5" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A5" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
-      <c r="L5" s="16"/>
-      <c r="M5" s="16"/>
-      <c r="N5" s="16"/>
-      <c r="O5" s="16"/>
-      <c r="P5" s="16"/>
-      <c r="Q5" s="16"/>
-    </row>
-    <row r="6" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
+      <c r="B5" s="32"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="32"/>
+      <c r="J5" s="32"/>
+      <c r="K5" s="32"/>
+      <c r="L5" s="32"/>
+      <c r="M5" s="32"/>
+      <c r="N5" s="32"/>
+      <c r="O5" s="32"/>
+      <c r="P5" s="32"/>
+      <c r="Q5" s="32"/>
+      <c r="R5" s="32"/>
+    </row>
+    <row r="6" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="13"/>
-    </row>
-    <row r="7" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+      <c r="B6" s="29"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="29"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="29"/>
+      <c r="N6" s="29"/>
+      <c r="O6" s="29"/>
+      <c r="P6" s="29"/>
+      <c r="Q6" s="29"/>
+      <c r="R6" s="29"/>
+    </row>
+    <row r="7" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="17"/>
-      <c r="N7" s="17"/>
-      <c r="O7" s="17"/>
-      <c r="P7" s="17"/>
-      <c r="Q7" s="17"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="14"/>
+      <c r="N7" s="14"/>
+      <c r="O7" s="14"/>
+      <c r="P7" s="14"/>
+      <c r="Q7" s="14"/>
+      <c r="R7" s="14"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A8" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21" t="s">
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="H8" s="21"/>
-      <c r="I8" s="21"/>
-      <c r="J8" s="21"/>
-      <c r="K8" s="21"/>
-      <c r="L8" s="21"/>
-      <c r="M8" s="21"/>
-      <c r="N8" s="21"/>
-      <c r="O8" s="21"/>
-      <c r="P8" s="22" t="s">
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="18"/>
+      <c r="N8" s="18"/>
+      <c r="O8" s="18"/>
+      <c r="P8" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="Q8" s="25" t="s">
+      <c r="Q8" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="R8" s="22" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="19"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="26" t="s">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A9" s="16"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="H9" s="27"/>
-      <c r="I9" s="27"/>
-      <c r="J9" s="27"/>
-      <c r="K9" s="28"/>
-      <c r="L9" s="29" t="s">
+      <c r="H9" s="24"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="M9" s="30"/>
-      <c r="N9" s="30"/>
-      <c r="O9" s="31"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="25"/>
-    </row>
-    <row r="10" spans="1:17" ht="42.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="20"/>
+      <c r="M9" s="27"/>
+      <c r="N9" s="27"/>
+      <c r="O9" s="28"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="22"/>
+      <c r="R9" s="22"/>
+    </row>
+    <row r="10" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="17"/>
       <c r="B10" s="4" t="s">
         <v>9</v>
       </c>
@@ -956,10 +976,11 @@
       <c r="O10" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P10" s="24"/>
-      <c r="Q10" s="25"/>
-    </row>
-    <row r="11" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P10" s="21"/>
+      <c r="Q10" s="22"/>
+      <c r="R10" s="22"/>
+    </row>
+    <row r="11" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>35</v>
       </c>
@@ -1008,11 +1029,14 @@
       <c r="P11" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="Q11" s="12" t="s">
+      <c r="Q11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="R11" s="12" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -1029,24 +1053,26 @@
       <c r="N12" s="11"/>
       <c r="O12" s="10"/>
       <c r="P12" s="6"/>
-      <c r="Q12" s="12"/>
+      <c r="Q12" s="6"/>
+      <c r="R12" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A7:Q7"/>
+  <mergeCells count="15">
+    <mergeCell ref="A6:R6"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A5:R5"/>
+    <mergeCell ref="A7:R7"/>
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="B8:F9"/>
     <mergeCell ref="G8:O8"/>
     <mergeCell ref="P8:P10"/>
-    <mergeCell ref="Q8:Q10"/>
+    <mergeCell ref="R8:R10"/>
     <mergeCell ref="G9:K9"/>
     <mergeCell ref="L9:O9"/>
-    <mergeCell ref="A6:Q6"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="A2:O2"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A5:Q5"/>
+    <mergeCell ref="Q8:Q10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
